--- a/test.xlsx
+++ b/test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Divyesh\IFC\AmazonDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0C1FDD-7C95-4D53-8A47-E288362B5F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E40AD1-BF55-4DC2-B925-203282385A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fixed Assets" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
   <si>
     <t>Yes</t>
   </si>
@@ -263,7 +263,7 @@
     <t>Process Owner</t>
   </si>
   <si>
-    <t>xyz@gmail.com</t>
+    <t>abcd12345</t>
   </si>
 </sst>
 </file>
@@ -1977,7 +1977,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AD7" r:id="rId1" xr:uid="{54CAC7B9-8D0C-42DC-9450-842F67D0D808}"/>
+    <hyperlink ref="AD7" r:id="rId1" display="xyz@gmail.com" xr:uid="{54CAC7B9-8D0C-42DC-9450-842F67D0D808}"/>
   </hyperlinks>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup scale="22" orientation="landscape" r:id="rId2"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Divyesh\IFC\AmazonDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E40AD1-BF55-4DC2-B925-203282385A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73852E40-31B8-443A-857D-8749D6BFEF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,9 +70,6 @@
     <t>Fixed Asset/CWIP/Depreciation</t>
   </si>
   <si>
-    <t>A budget for fixed asset procurement is prepared for the acquisitions during the year. The budget is approved by top management</t>
-  </si>
-  <si>
     <t>Adequate budgetary provisions are done</t>
   </si>
   <si>
@@ -251,9 +248,6 @@
     </r>
   </si>
   <si>
-    <t>Fortnightly</t>
-  </si>
-  <si>
     <t>Risk Heat</t>
   </si>
   <si>
@@ -263,7 +257,13 @@
     <t>Process Owner</t>
   </si>
   <si>
-    <t>abcd12345</t>
+    <t>Testing of process owner on excel file upload. Also reminder frequency</t>
+  </si>
+  <si>
+    <t>divyeshparmar0909@gmail.com</t>
+  </si>
+  <si>
+    <t>Weekly</t>
   </si>
 </sst>
 </file>
@@ -965,12 +965,12 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
       <c r="D1" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
@@ -1001,12 +1001,12 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="46"/>
       <c r="C2" s="46"/>
       <c r="D2" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -1018,7 +1018,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O2" s="2">
         <v>8</v>
@@ -1041,12 +1041,12 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="46"/>
       <c r="C3" s="46"/>
       <c r="D3" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1058,7 +1058,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O3" s="2">
         <v>5</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -1121,14 +1121,14 @@
       <c r="E5" s="47"/>
       <c r="F5" s="37"/>
       <c r="G5" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="47"/>
       <c r="I5" s="47"/>
       <c r="J5" s="47"/>
       <c r="K5" s="47"/>
       <c r="L5" s="45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M5" s="45"/>
       <c r="N5" s="45"/>
@@ -1145,7 +1145,7 @@
       <c r="Y5" s="45"/>
       <c r="Z5" s="45"/>
       <c r="AA5" s="45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AB5" s="45"/>
       <c r="AC5" s="45"/>
@@ -1153,99 +1153,99 @@
     </row>
     <row r="6" spans="1:31" s="5" customFormat="1" ht="120.75" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="R6" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="S6" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="T6" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="U6" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="V6" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="W6" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="X6" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y6" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z6" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA6" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB6" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC6" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD6" s="28" t="s">
         <v>59</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="P6" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="R6" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="S6" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="T6" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="U6" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="V6" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="W6" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="X6" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y6" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z6" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA6" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB6" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC6" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD6" s="28" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>5</v>
@@ -1254,49 +1254,49 @@
         <v>4</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="M7" s="32" t="s">
-        <v>6</v>
-      </c>
       <c r="N7" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P7" s="16" t="s">
         <v>0</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S7" s="17" t="s">
         <v>2</v>
@@ -1308,31 +1308,31 @@
         <v>0</v>
       </c>
       <c r="V7" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" s="17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="X7" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y7" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z7" s="17" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AC7" s="36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AD7" s="42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AE7" s="44"/>
     </row>
@@ -1977,7 +1977,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AD7" r:id="rId1" display="xyz@gmail.com" xr:uid="{54CAC7B9-8D0C-42DC-9450-842F67D0D808}"/>
+    <hyperlink ref="AD7" r:id="rId1" xr:uid="{54CAC7B9-8D0C-42DC-9450-842F67D0D808}"/>
   </hyperlinks>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup scale="22" orientation="landscape" r:id="rId2"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Divyesh\IFC\AmazonDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73852E40-31B8-443A-857D-8749D6BFEF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A18E332-F9B4-4AF3-8571-46772129706E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>Yes</t>
   </si>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>Control number</t>
-  </si>
-  <si>
-    <t>Design and implementation</t>
   </si>
   <si>
     <t>Control</t>
@@ -254,16 +251,13 @@
     <t>High</t>
   </si>
   <si>
-    <t>Process Owner</t>
-  </si>
-  <si>
     <t>Testing of process owner on excel file upload. Also reminder frequency</t>
   </si>
   <si>
-    <t>divyeshparmar0909@gmail.com</t>
-  </si>
-  <si>
     <t>Weekly</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -434,7 +428,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -577,6 +571,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -965,12 +962,12 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
       <c r="D1" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
@@ -1001,12 +998,12 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="46"/>
       <c r="C2" s="46"/>
       <c r="D2" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -1018,7 +1015,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O2" s="2">
         <v>8</v>
@@ -1041,12 +1038,12 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="46"/>
       <c r="C3" s="46"/>
       <c r="D3" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1058,7 +1055,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O3" s="2">
         <v>5</v>
@@ -1113,7 +1110,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -1121,14 +1118,14 @@
       <c r="E5" s="47"/>
       <c r="F5" s="37"/>
       <c r="G5" s="47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5" s="47"/>
       <c r="I5" s="47"/>
       <c r="J5" s="47"/>
       <c r="K5" s="47"/>
       <c r="L5" s="45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M5" s="45"/>
       <c r="N5" s="45"/>
@@ -1144,9 +1141,7 @@
       <c r="X5" s="45"/>
       <c r="Y5" s="45"/>
       <c r="Z5" s="45"/>
-      <c r="AA5" s="45" t="s">
-        <v>33</v>
-      </c>
+      <c r="AA5" s="45"/>
       <c r="AB5" s="45"/>
       <c r="AC5" s="45"/>
       <c r="AD5" s="45"/>
@@ -1168,7 +1163,7 @@
         <v>28</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6" s="29" t="s">
         <v>27</v>
@@ -1192,10 +1187,10 @@
         <v>21</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O6" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P6" s="28" t="s">
         <v>20</v>
@@ -1222,10 +1217,10 @@
         <v>13</v>
       </c>
       <c r="X6" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y6" s="28" t="s">
         <v>40</v>
-      </c>
-      <c r="Y6" s="28" t="s">
-        <v>41</v>
       </c>
       <c r="Z6" s="41" t="s">
         <v>12</v>
@@ -1239,13 +1234,11 @@
       <c r="AC6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="AD6" s="28" t="s">
-        <v>59</v>
-      </c>
+      <c r="AD6" s="28"/>
     </row>
     <row r="7" spans="1:31" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>5</v>
@@ -1260,43 +1253,35 @@
         <v>7</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="43" t="s">
-        <v>23</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="G7" s="43"/>
+      <c r="H7" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
       <c r="L7" s="31" t="s">
         <v>6</v>
       </c>
       <c r="M7" s="32" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P7" s="16" t="s">
         <v>0</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S7" s="17" t="s">
         <v>2</v>
@@ -1308,32 +1293,30 @@
         <v>0</v>
       </c>
       <c r="V7" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W7" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="X7" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y7" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z7" s="17" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AC7" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD7" s="42" t="s">
-        <v>61</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AD7" s="42"/>
       <c r="AE7" s="44"/>
     </row>
     <row r="8" spans="1:31" ht="14.25" x14ac:dyDescent="0.2">
@@ -1976,11 +1959,8 @@
       <formula1>"P, O"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="AD7" r:id="rId1" xr:uid="{54CAC7B9-8D0C-42DC-9450-842F67D0D808}"/>
-  </hyperlinks>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup scale="22" orientation="landscape" r:id="rId2"/>
+  <pageSetup scale="22" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;C&amp;"-,Bold"Gujarat Fluorochemicals Limited</oddHeader>
     <oddFooter>&amp;C&amp;"-,Italic"&amp;9&amp;K00-033Private and Confidential&amp;R&amp;"Calibri,Regular"&amp;9&amp;P</oddFooter>

--- a/test.xlsx
+++ b/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Divyesh\IFC\AmazonDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A18E332-F9B4-4AF3-8571-46772129706E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284E7E9F-42CB-4294-831D-C92ED0B0DF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,6 +562,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -571,9 +574,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -961,11 +961,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
       <c r="D1" s="26" t="s">
         <v>53</v>
       </c>
@@ -997,11 +997,11 @@
       <c r="AD1" s="2"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
       <c r="D2" s="27" t="s">
         <v>49</v>
       </c>
@@ -1037,11 +1037,11 @@
       <c r="AD2" s="2"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
       <c r="D3" s="12" t="s">
         <v>36</v>
       </c>
@@ -1109,42 +1109,42 @@
       <c r="AD4" s="2"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
       <c r="F5" s="37"/>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="45" t="s">
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="45"/>
-      <c r="U5" s="45"/>
-      <c r="V5" s="45"/>
-      <c r="W5" s="45"/>
-      <c r="X5" s="45"/>
-      <c r="Y5" s="45"/>
-      <c r="Z5" s="45"/>
-      <c r="AA5" s="45"/>
-      <c r="AB5" s="45"/>
-      <c r="AC5" s="45"/>
-      <c r="AD5" s="45"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+      <c r="Y5" s="46"/>
+      <c r="Z5" s="46"/>
+      <c r="AA5" s="46"/>
+      <c r="AB5" s="46"/>
+      <c r="AC5" s="46"/>
+      <c r="AD5" s="46"/>
     </row>
     <row r="6" spans="1:31" s="5" customFormat="1" ht="120.75" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
@@ -1256,7 +1256,7 @@
         <v>57</v>
       </c>
       <c r="G7" s="43"/>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="45" t="s">
         <v>60</v>
       </c>
       <c r="I7" s="43"/>
